--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_46.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4115958.767684798</v>
+        <v>4152316.813992016</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13275569.19337384</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13275569.19337384</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117042476</v>
+        <v>603.5370117034352</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117042476</v>
+        <v>603.5370117034352</v>
       </c>
     </row>
     <row r="11">
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>321.9805303958886</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>19.47719999075348</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -793,13 +793,13 @@
         <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>164.5507292321765</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -988,7 +988,7 @@
         <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>19.47719999075348</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>133.6519859716245</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -1225,7 +1225,7 @@
         <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716245</v>
+        <v>134.7013707387712</v>
       </c>
       <c r="S9" t="n">
         <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>181.6470893908422</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
         <v>0.1959257979225981</v>
@@ -1380,7 +1380,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S11" t="n">
         <v>142.3350019731772</v>
@@ -1422,7 +1422,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.5712507480957</v>
+        <v>328.1106633827815</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1450,19 +1450,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>26.93768689770263</v>
+        <v>200.5295027796757</v>
       </c>
       <c r="E12" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1495,25 +1495,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>305.4120422616788</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1565,16 +1565,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1684,22 +1684,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>177.5914272286982</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1744,10 +1744,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>111.3731429098285</v>
+        <v>284.9649587918013</v>
       </c>
       <c r="X15" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
         <v>78.39139276613435</v>
@@ -1802,7 +1802,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627038</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
@@ -1811,7 +1811,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G17" t="n">
         <v>81.3744577141519</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1918,22 +1918,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>3.99961134672543</v>
+        <v>177.5914272286985</v>
       </c>
       <c r="H18" t="n">
         <v>4.021973978873973</v>
@@ -1972,7 +1972,7 @@
         <v>131.8202263797057</v>
       </c>
       <c r="T18" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U18" t="n">
         <v>79.16168051490371</v>
@@ -1981,10 +1981,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>284.9649587918013</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
         <v>78.39139276613435</v>
@@ -2027,13 +2027,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N19" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O19" t="n">
         <v>231.765039488851</v>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>213.6917283274922</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
         <v>3.99961134672543</v>
@@ -2224,7 +2224,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481071</v>
       </c>
     </row>
     <row r="22">
@@ -2316,7 +2316,7 @@
         <v>160.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>128.4745782429939</v>
+        <v>128.9351656083081</v>
       </c>
       <c r="D23" t="n">
         <v>89.33915573984979</v>
@@ -2331,7 +2331,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.999611346725456</v>
+        <v>98.96287911935113</v>
       </c>
       <c r="H24" t="n">
-        <v>98.98524175149964</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H26" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U26" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
         <v>40.09991244551929</v>
@@ -2641,16 +2641,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I27" t="n">
-        <v>173.5918158819732</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2695,10 +2695,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481075</v>
       </c>
     </row>
     <row r="28">
@@ -2802,10 +2802,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>158.5198244189526</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>324.9996113467254</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,19 +2911,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N31" t="n">
         <v>155.2579933044718</v>
@@ -2987,16 +2987,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S31" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3039,13 +3039,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H32" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -3118,10 +3118,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>177.5914272286982</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3154,13 +3154,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M34" t="n">
         <v>102.3923982877958</v>
@@ -3224,16 +3224,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S34" t="n">
-        <v>29.72461090246172</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
         <v>72.84688483418068</v>
@@ -3340,28 +3340,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C36" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9996113467254</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I36" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,19 +3385,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
-        <v>305.6877037025646</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
         <v>93.51066719152016</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T38" t="n">
         <v>259.6218731858503</v>
@@ -3586,7 +3586,7 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -3598,7 +3598,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I39" t="n">
-        <v>173.5918158819732</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3637,7 +3637,7 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V39" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
         <v>111.3731429098285</v>
@@ -3646,7 +3646,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481074</v>
       </c>
     </row>
     <row r="40">
@@ -3707,7 +3707,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090247624</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3814,16 +3814,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>21.67209722191262</v>
+        <v>195.2639131038857</v>
       </c>
       <c r="F42" t="n">
         <v>18.63624233787687</v>
@@ -3835,7 +3835,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,16 +3859,16 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>404.6459244566755</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
         <v>79.16168051490372</v>
@@ -3944,7 +3944,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090251361</v>
+        <v>29.72461090251316</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,13 +3987,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>40.09991244551929</v>
@@ -4066,10 +4066,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,19 +4096,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>402.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4117,10 +4117,10 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>98.86273944538755</v>
+        <v>193.8260072180132</v>
       </c>
       <c r="Y45" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,13 +4172,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>376.8716854102422</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S46" t="n">
         <v>30.56285675203577</v>
@@ -4321,22 +4321,22 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>451.8183303517587</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>822.0783303517587</v>
+        <v>385.22</v>
       </c>
       <c r="M2" t="n">
-        <v>1067.648108133742</v>
+        <v>755.48</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.648108133742</v>
+        <v>755.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>755.48</v>
       </c>
       <c r="P2" t="n">
         <v>1125.74</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1075.987801776748</v>
+        <v>29.92</v>
       </c>
       <c r="C3" t="n">
-        <v>1075.987801776748</v>
+        <v>29.92</v>
       </c>
       <c r="D3" t="n">
-        <v>724.5355927891701</v>
+        <v>29.92</v>
       </c>
       <c r="E3" t="n">
-        <v>378.4021612518846</v>
+        <v>29.92</v>
       </c>
       <c r="F3" t="n">
-        <v>378.4021612518846</v>
+        <v>29.92</v>
       </c>
       <c r="G3" t="n">
-        <v>49.59393938459948</v>
+        <v>29.92</v>
       </c>
       <c r="H3" t="n">
-        <v>49.59393938459948</v>
+        <v>29.92</v>
       </c>
       <c r="I3" t="n">
         <v>29.92</v>
@@ -4436,16 +4436,16 @@
         <v>1143.408558894664</v>
       </c>
       <c r="V3" t="n">
-        <v>1128.75131930727</v>
+        <v>765.6307811168861</v>
       </c>
       <c r="W3" t="n">
-        <v>1096.051174953908</v>
+        <v>732.9306367635239</v>
       </c>
       <c r="X3" t="n">
-        <v>1075.987801776748</v>
+        <v>355.1528589857461</v>
       </c>
       <c r="Y3" t="n">
-        <v>1075.987801776748</v>
+        <v>355.1528589857461</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.92</v>
+        <v>1319.501038929473</v>
       </c>
       <c r="C4" t="n">
-        <v>29.92</v>
+        <v>1445.503044747909</v>
       </c>
       <c r="D4" t="n">
-        <v>87.67946781506721</v>
+        <v>1496</v>
       </c>
       <c r="E4" t="n">
-        <v>205.5083720264802</v>
+        <v>1496</v>
       </c>
       <c r="F4" t="n">
-        <v>329.8693446184157</v>
+        <v>1496</v>
       </c>
       <c r="G4" t="n">
-        <v>483.4580055872682</v>
+        <v>1496</v>
       </c>
       <c r="H4" t="n">
-        <v>654.5935815663379</v>
+        <v>1496</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401257</v>
+        <v>1496</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1496</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1496</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1496</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1403.273682802524</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1258.790761928658</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>1042.177358901337</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>774.2966876474056</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>460.7236912579127</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>139.176451535273</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>139.176451535273</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>328.0301733170287</v>
       </c>
       <c r="U4" t="n">
-        <v>29.92</v>
+        <v>574.5912984143317</v>
       </c>
       <c r="V4" t="n">
-        <v>29.92</v>
+        <v>773.4126913002776</v>
       </c>
       <c r="W4" t="n">
-        <v>29.92</v>
+        <v>945.303609559955</v>
       </c>
       <c r="X4" t="n">
-        <v>29.92</v>
+        <v>1096.334400584149</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.92</v>
+        <v>1207.743701263181</v>
       </c>
     </row>
     <row r="5">
@@ -4558,16 +4558,16 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>327.1281081337421</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>697.3881081337421</v>
       </c>
       <c r="L5" t="n">
-        <v>464.2419149748744</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="M5" t="n">
-        <v>834.5019149748744</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N5" t="n">
         <v>1067.648108133742</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1075.987801776748</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="C6" t="n">
-        <v>1075.987801776748</v>
+        <v>1056.313862392149</v>
       </c>
       <c r="D6" t="n">
-        <v>724.5355927891701</v>
+        <v>704.8616534045707</v>
       </c>
       <c r="E6" t="n">
-        <v>378.4021612518846</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="F6" t="n">
-        <v>378.4021612518846</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="G6" t="n">
-        <v>49.59393938459948</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U6" t="n">
-        <v>1143.408558894664</v>
+        <v>1289.947477320344</v>
       </c>
       <c r="V6" t="n">
-        <v>1128.75131930727</v>
+        <v>1275.29023773295</v>
       </c>
       <c r="W6" t="n">
-        <v>1096.051174953908</v>
+        <v>1242.590093379587</v>
       </c>
       <c r="X6" t="n">
-        <v>1075.987801776748</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="Y6" t="n">
-        <v>1075.987801776748</v>
+        <v>1222.526720202428</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218.6183178716313</v>
+        <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>344.620323690067</v>
+        <v>155.9220058184358</v>
       </c>
       <c r="D7" t="n">
-        <v>457.9394678150671</v>
+        <v>269.2411499434359</v>
       </c>
       <c r="E7" t="n">
-        <v>575.7683720264802</v>
+        <v>387.0700541548489</v>
       </c>
       <c r="F7" t="n">
-        <v>700.1293446184156</v>
+        <v>511.4310267467844</v>
       </c>
       <c r="G7" t="n">
-        <v>853.7180055872682</v>
+        <v>665.0196877156368</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.853581566338</v>
+        <v>836.1552636947065</v>
       </c>
       <c r="I7" t="n">
-        <v>1251.462556240126</v>
+        <v>1062.764238368494</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4761,7 +4761,7 @@
         <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>106.8609802053391</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="8">
@@ -4804,16 +4804,16 @@
         <v>451.8183303517587</v>
       </c>
       <c r="M8" t="n">
-        <v>697.388108133742</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1192.338330351759</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1192.338330351759</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1250.430222218017</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1043.563442497332</v>
+        <v>1074.927817163469</v>
       </c>
       <c r="C9" t="n">
-        <v>1043.563442497332</v>
+        <v>710.1804308548635</v>
       </c>
       <c r="D9" t="n">
-        <v>692.1112335097536</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="E9" t="n">
-        <v>692.1112335097536</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="F9" t="n">
-        <v>692.1112335097536</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="G9" t="n">
-        <v>363.3030116424684</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1210.185121297632</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1147.065109898273</v>
       </c>
       <c r="T9" t="n">
-        <v>1111.182104461634</v>
+        <v>1142.546479127771</v>
       </c>
       <c r="U9" t="n">
-        <v>1110.984199615247</v>
+        <v>1142.348574281384</v>
       </c>
       <c r="V9" t="n">
-        <v>1096.326960027853</v>
+        <v>1127.69133469399</v>
       </c>
       <c r="W9" t="n">
-        <v>1063.626815674491</v>
+        <v>1094.991190340628</v>
       </c>
       <c r="X9" t="n">
-        <v>1043.563442497332</v>
+        <v>1074.927817163469</v>
       </c>
       <c r="Y9" t="n">
-        <v>1043.563442497332</v>
+        <v>1074.927817163469</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>370.6066982106988</v>
+        <v>909.6335279461522</v>
       </c>
       <c r="C10" t="n">
-        <v>370.6066982106988</v>
+        <v>909.6335279461522</v>
       </c>
       <c r="D10" t="n">
-        <v>457.9394678150671</v>
+        <v>1022.952672071152</v>
       </c>
       <c r="E10" t="n">
-        <v>575.7683720264802</v>
+        <v>1022.952672071152</v>
       </c>
       <c r="F10" t="n">
-        <v>700.1293446184156</v>
+        <v>1147.313644663088</v>
       </c>
       <c r="G10" t="n">
-        <v>853.7180055872682</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="H10" t="n">
-        <v>1024.853581566338</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240126</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>259.1973975316665</v>
+        <v>276.481125097303</v>
       </c>
       <c r="V10" t="n">
-        <v>259.1973975316665</v>
+        <v>475.302517983249</v>
       </c>
       <c r="W10" t="n">
-        <v>259.1973975316665</v>
+        <v>647.1934362429264</v>
       </c>
       <c r="X10" t="n">
-        <v>259.1973975316665</v>
+        <v>798.2242272671199</v>
       </c>
       <c r="Y10" t="n">
-        <v>370.6066982106988</v>
+        <v>909.6335279461522</v>
       </c>
     </row>
     <row r="11">
@@ -5020,7 +5020,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F11" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G11" t="n">
         <v>125.5027119537179</v>
@@ -5035,10 +5035,10 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>737.2059437357115</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L11" t="n">
-        <v>953.2578922784251</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M11" t="n">
         <v>1595.767892278425</v>
@@ -5056,13 +5056,13 @@
         <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S11" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U11" t="n">
         <v>1858.092802114017</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>168.4528527561725</v>
+        <v>992.2829698086706</v>
       </c>
       <c r="C12" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424895</v>
       </c>
       <c r="D12" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E12" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F12" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5138,25 +5138,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S12" t="n">
-        <v>1753.535205884733</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T12" t="n">
-        <v>1347.095458285567</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U12" t="n">
-        <v>942.8917405937456</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V12" t="n">
-        <v>848.4365212083717</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W12" t="n">
-        <v>735.9383970570298</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X12" t="n">
-        <v>636.0770440818908</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y12" t="n">
-        <v>232.6513948231691</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="13">
@@ -5196,25 +5196,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5269,25 +5269,25 @@
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>737.2059437357115</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L14" t="n">
-        <v>953.2578922784251</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M14" t="n">
-        <v>1595.767892278425</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N14" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O14" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1316.525394051095</v>
+        <v>816.9377012410212</v>
       </c>
       <c r="C15" t="n">
-        <v>1276.020431984914</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D15" t="n">
-        <v>924.5682229973352</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
-        <v>578.4347914600496</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F15" t="n">
-        <v>235.3678800076487</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866058</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5387,13 +5387,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X15" t="n">
-        <v>1459.907161134389</v>
+        <v>960.319468324315</v>
       </c>
       <c r="Y15" t="n">
-        <v>1380.723936118091</v>
+        <v>881.1362433080177</v>
       </c>
     </row>
     <row r="16">
@@ -5445,13 +5445,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R16" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F17" t="n">
         <v>207.6991338872047</v>
@@ -5521,37 +5521,37 @@
         <v>1808.651587033441</v>
       </c>
       <c r="O17" t="n">
-        <v>2399.40799366138</v>
+        <v>1969.781688416396</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2166.373694755016</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="18">
@@ -5561,19 +5561,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>492.6952769985969</v>
+        <v>992.2829698086706</v>
       </c>
       <c r="C18" t="n">
-        <v>452.1903149324157</v>
+        <v>627.5355835000653</v>
       </c>
       <c r="D18" t="n">
-        <v>424.9805301872615</v>
+        <v>276.0833745124868</v>
       </c>
       <c r="E18" t="n">
-        <v>78.84709864997603</v>
+        <v>254.1923672176256</v>
       </c>
       <c r="F18" t="n">
-        <v>60.0226114399994</v>
+        <v>235.367880007649</v>
       </c>
       <c r="G18" t="n">
         <v>55.98259997866058</v>
@@ -5615,22 +5615,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T18" t="n">
-        <v>1846.683151095641</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U18" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V18" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W18" t="n">
-        <v>1384.423245541878</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X18" t="n">
-        <v>960.319468324315</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y18" t="n">
-        <v>881.1362433080177</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="19">
@@ -5670,10 +5670,10 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M19" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N19" t="n">
         <v>1349.248439584877</v>
@@ -5752,16 +5752,16 @@
         <v>523.631587033441</v>
       </c>
       <c r="M20" t="n">
-        <v>1166.141587033441</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N20" t="n">
-        <v>1808.651587033441</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O20" t="n">
-        <v>1969.781688416396</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P20" t="n">
-        <v>2166.373694755016</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1316.525394051095</v>
+        <v>816.9377012410212</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.675163417264</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D21" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E21" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F21" t="n">
         <v>60.0226114399994</v>
@@ -5867,7 +5867,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y21" t="n">
-        <v>1380.723936118091</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="22">
@@ -5959,19 +5959,19 @@
         <v>597.1205880922939</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5989,13 +5989,13 @@
         <v>523.631587033441</v>
       </c>
       <c r="M23" t="n">
-        <v>1166.141587033441</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N23" t="n">
-        <v>1205.91497964478</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O23" t="n">
-        <v>1367.045081027735</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P23" t="n">
         <v>2009.555081027735</v>
@@ -6050,7 +6050,7 @@
         <v>155.9451041396213</v>
       </c>
       <c r="G24" t="n">
-        <v>151.9050926782825</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D26" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H26" t="n">
         <v>51.92</v>
@@ -6217,25 +6217,25 @@
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L26" t="n">
-        <v>949.6332762537361</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M26" t="n">
-        <v>1592.143276253736</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N26" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O26" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P26" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
@@ -6250,19 +6250,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="27">
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>992.2829698086707</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C27" t="n">
-        <v>951.7780077424896</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D27" t="n">
-        <v>924.5682229973355</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E27" t="n">
-        <v>578.4347914600501</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F27" t="n">
-        <v>559.6103042500735</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G27" t="n">
-        <v>555.5702927887346</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H27" t="n">
-        <v>227.2652685676497</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6338,10 +6338,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X27" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y27" t="n">
-        <v>1380.723936118092</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="28">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C29" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D29" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E29" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F29" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G29" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H29" t="n">
         <v>51.92</v>
@@ -6454,52 +6454,52 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L29" t="n">
-        <v>949.6332762537361</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M29" t="n">
-        <v>1149.849898617045</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N29" t="n">
-        <v>1792.359898617045</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O29" t="n">
-        <v>1953.49</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S29" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W29" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X29" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1141.180125483445</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C30" t="n">
-        <v>776.4327391748399</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D30" t="n">
-        <v>749.2229544296857</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E30" t="n">
-        <v>727.3319471348245</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F30" t="n">
-        <v>384.2650356824237</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6554,31 +6554,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R30" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S30" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U30" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W30" t="n">
-        <v>1480.3457382415</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X30" t="n">
-        <v>1380.484385266361</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y30" t="n">
-        <v>1301.301160250064</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="31">
@@ -6621,22 +6621,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N31" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O31" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P31" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R31" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D32" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H32" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I32" t="n">
         <v>51.92</v>
@@ -6697,19 +6697,19 @@
         <v>307.5796384907274</v>
       </c>
       <c r="L32" t="n">
-        <v>523.631587033441</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M32" t="n">
-        <v>1166.141587033441</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N32" t="n">
-        <v>1651.83297330616</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O32" t="n">
-        <v>1812.963074689115</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P32" t="n">
-        <v>2009.555081027735</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6727,16 +6727,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W32" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="33">
@@ -6749,19 +6749,19 @@
         <v>1316.525394051095</v>
       </c>
       <c r="C33" t="n">
-        <v>1276.020431984914</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D33" t="n">
-        <v>924.5682229973352</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E33" t="n">
-        <v>578.4347914600496</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F33" t="n">
-        <v>235.3678800076487</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G33" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6800,7 +6800,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U33" t="n">
         <v>1766.721857646244</v>
@@ -6815,7 +6815,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y33" t="n">
-        <v>1380.723936118091</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="34">
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>686.6440969024205</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C34" t="n">
-        <v>734.4361027208563</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D34" t="n">
-        <v>769.5452468458564</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E34" t="n">
-        <v>809.1641510572694</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F34" t="n">
-        <v>855.3151236492048</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G34" t="n">
-        <v>931.125814126254</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H34" t="n">
-        <v>1027.892525187291</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I34" t="n">
-        <v>1189.283805434849</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J34" t="n">
-        <v>1515.576154611891</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K34" t="n">
-        <v>1619.080700024169</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L34" t="n">
-        <v>1608.65464740578</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M34" t="n">
-        <v>1505.227982468612</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N34" t="n">
-        <v>1348.401726605509</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O34" t="n">
-        <v>1114.29562611172</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9299076645448</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.4700425881831</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R34" t="n">
-        <v>81.94485949743608</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6891,10 +6891,10 @@
         <v>547.0766675328789</v>
       </c>
       <c r="X34" t="n">
-        <v>619.8974585570961</v>
+        <v>619.8974585570725</v>
       </c>
       <c r="Y34" t="n">
-        <v>653.0967592361284</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="35">
@@ -6916,7 +6916,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G35" t="n">
         <v>125.5027119537179</v>
@@ -6928,25 +6928,25 @@
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L35" t="n">
-        <v>949.6332762537361</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M35" t="n">
-        <v>1592.143276253736</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N35" t="n">
-        <v>2234.653276253736</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O35" t="n">
-        <v>2395.783377636692</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P35" t="n">
-        <v>2592.375383975311</v>
+        <v>2596</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>686.2820590119658</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C36" t="n">
-        <v>645.7770969457847</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D36" t="n">
-        <v>618.5673122006306</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E36" t="n">
-        <v>596.6763049057694</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F36" t="n">
-        <v>577.8518176957928</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G36" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H36" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I36" t="n">
         <v>51.92</v>
@@ -7028,31 +7028,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S36" t="n">
-        <v>1525.215274341931</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1216.439816056512</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U36" t="n">
-        <v>1136.478522607115</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>1042.023303221741</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>929.5251790703986</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>829.6638260952597</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y36" t="n">
-        <v>750.4806010789623</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="37">
@@ -7104,13 +7104,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C38" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D38" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E38" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G38" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H38" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I38" t="n">
         <v>51.92</v>
@@ -7168,22 +7168,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L38" t="n">
-        <v>950.0896384907273</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.599638490728</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N38" t="n">
-        <v>2235.109638490728</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O38" t="n">
-        <v>2396.239739873683</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P38" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7192,25 +7192,25 @@
         <v>2596</v>
       </c>
       <c r="S38" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T38" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U38" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V38" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W38" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X38" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y38" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="39">
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>992.2829698086708</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C39" t="n">
-        <v>951.7780077424898</v>
+        <v>452.1903149324158</v>
       </c>
       <c r="D39" t="n">
-        <v>924.5682229973356</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E39" t="n">
-        <v>578.4347914600501</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
-        <v>235.3678800076491</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G39" t="n">
-        <v>231.3278685463103</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H39" t="n">
-        <v>227.2652685676497</v>
+        <v>51.92</v>
       </c>
       <c r="I39" t="n">
         <v>51.92</v>
@@ -7280,16 +7280,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W39" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X39" t="n">
-        <v>1135.664736891965</v>
+        <v>811.4223126495403</v>
       </c>
       <c r="Y39" t="n">
-        <v>1056.481511875667</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="40">
@@ -7323,31 +7323,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611905</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024183</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405794</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468627</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605524</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111735</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645594</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881978</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949745075</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D41" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7405,10 +7405,10 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>775.9368380887173</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L41" t="n">
-        <v>991.9887866314309</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M41" t="n">
         <v>1595.767892278425</v>
@@ -7426,28 +7426,28 @@
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>362.0396347695416</v>
+        <v>992.2829698086707</v>
       </c>
       <c r="C42" t="n">
-        <v>321.5346727033605</v>
+        <v>627.5355835000653</v>
       </c>
       <c r="D42" t="n">
-        <v>294.3248879582063</v>
+        <v>276.0833745124868</v>
       </c>
       <c r="E42" t="n">
-        <v>272.4338806633451</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F42" t="n">
-        <v>253.6093934533685</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G42" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H42" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7502,31 +7502,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>1756.031307473563</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S42" t="n">
-        <v>1298.637139413254</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T42" t="n">
-        <v>892.197391814088</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U42" t="n">
-        <v>812.2360983646903</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V42" t="n">
-        <v>717.7808789793164</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W42" t="n">
-        <v>605.2827548279745</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X42" t="n">
-        <v>505.4214018528356</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y42" t="n">
-        <v>426.2381768365382</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>686.6440969024725</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C43" t="n">
-        <v>734.4361027209083</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D43" t="n">
-        <v>769.5452468459083</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E43" t="n">
-        <v>809.1641510573213</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F43" t="n">
-        <v>855.3151236492567</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G43" t="n">
-        <v>931.125814126306</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H43" t="n">
-        <v>1027.892525187343</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I43" t="n">
-        <v>1189.283805434901</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J43" t="n">
         <v>1515.576154611943</v>
@@ -7572,19 +7572,19 @@
         <v>1505.227982468664</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605562</v>
+        <v>1348.401726605561</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111773</v>
+        <v>1114.295626111772</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645972</v>
+        <v>819.9299076645967</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425882356</v>
+        <v>463.4700425882351</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949748849</v>
+        <v>81.94485949748804</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7596,16 +7596,16 @@
         <v>332.7843563872555</v>
       </c>
       <c r="V43" t="n">
-        <v>453.3957492732771</v>
+        <v>453.3957492732014</v>
       </c>
       <c r="W43" t="n">
-        <v>547.0766675329545</v>
+        <v>547.0766675328789</v>
       </c>
       <c r="X43" t="n">
-        <v>619.8974585571481</v>
+        <v>619.8974585570725</v>
       </c>
       <c r="Y43" t="n">
-        <v>653.0967592361803</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="44">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D44" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H44" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
@@ -7642,19 +7642,19 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>668.47</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M44" t="n">
-        <v>1310.98</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N44" t="n">
-        <v>1310.98</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O44" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P44" t="n">
         <v>2596</v>
@@ -7663,28 +7663,28 @@
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S44" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W44" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="45">
@@ -7706,10 +7706,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F45" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H45" t="n">
         <v>51.92</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R45" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S45" t="n">
-        <v>1604.638050209959</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T45" t="n">
-        <v>1198.198302610793</v>
+        <v>1443.01795098519</v>
       </c>
       <c r="U45" t="n">
-        <v>1118.237009161395</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V45" t="n">
-        <v>1023.781789776021</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W45" t="n">
-        <v>587.0412413822548</v>
+        <v>831.8608897566517</v>
       </c>
       <c r="X45" t="n">
-        <v>487.1798884071159</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y45" t="n">
-        <v>407.9966633908185</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="46">
@@ -7815,10 +7815,10 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
         <v>82.79157247680381</v>
@@ -7964,16 +7964,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748744</v>
+        <v>242.0199542155221</v>
       </c>
       <c r="M2" t="n">
-        <v>720.3111720492747</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
         <v>404.0826666125488</v>
@@ -7982,7 +7982,7 @@
         <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>315.3213213472141</v>
       </c>
       <c r="Q2" t="n">
         <v>502.5418702571336</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>300.4507139686307</v>
       </c>
       <c r="K5" t="n">
         <v>321.8400703517588</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>472.2608914614128</v>
       </c>
       <c r="N5" t="n">
-        <v>639.5838718235262</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8447,7 +8447,7 @@
         <v>309.2909949748744</v>
       </c>
       <c r="M8" t="n">
-        <v>720.3111720492745</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
         <v>778.0826666125488</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>376.5921508449956</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,13 +8678,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>433.9659648939233</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>950.4344291498551</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N11" t="n">
         <v>879.4920535472222</v>
@@ -8912,16 +8912,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>433.9659648939233</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>950.4344291498551</v>
+        <v>361.7270524351312</v>
       </c>
       <c r="N14" t="n">
         <v>879.4920535472222</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9164,13 +9164,13 @@
         <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
-        <v>433.9659648939237</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.48346824708341</v>
+        <v>457.4494331410071</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N20" t="n">
         <v>879.4920535472222</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>457.4494331410071</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9632,16 +9632,16 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>950.4344291498551</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N23" t="n">
-        <v>270.6671975990795</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>950.4344291498551</v>
+        <v>911.3123136417682</v>
       </c>
       <c r="N26" t="n">
-        <v>290.7846768324985</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10106,10 +10106,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>503.6734416380457</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>879.4920535472222</v>
+        <v>270.6671975990795</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>450.422215819576</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,13 +10340,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M32" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>721.0894134186553</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,10 +10571,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,16 +10583,16 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>879.4920535472222</v>
+        <v>354.1276162037367</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>27.14469655484982</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,25 +10811,25 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>517.5214927997022</v>
       </c>
       <c r="N38" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q38" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,13 +11048,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>473.0880804020101</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>911.3123136417682</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
         <v>879.4920535472222</v>
@@ -11285,22 +11285,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
-        <v>146.3014272389486</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>230.4920535472222</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O44" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>23.48346824708341</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23660,7 +23660,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23885,13 +23885,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -24836,7 +24836,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8382458495740472</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495595273</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495221599</v>
+        <v>0.8382458495226111</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26269,16 +26269,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1448283.596382485</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1448283.596382485</v>
+      </c>
+      <c r="D2" t="n">
         <v>1448283.596382484</v>
       </c>
-      <c r="C2" t="n">
-        <v>1448283.596382484</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1448283.596382485</v>
-      </c>
       <c r="E2" t="n">
-        <v>1448260.460797034</v>
+        <v>1448260.460797035</v>
       </c>
       <c r="F2" t="n">
         <v>1448260.460797035</v>
@@ -26293,19 +26293,19 @@
         <v>1448260.460797035</v>
       </c>
       <c r="J2" t="n">
-        <v>1448260.460797035</v>
+        <v>1448260.460797034</v>
       </c>
       <c r="K2" t="n">
         <v>1448260.460797035</v>
       </c>
       <c r="L2" t="n">
+        <v>1448260.460797035</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1448260.460797034</v>
+      </c>
+      <c r="N2" t="n">
         <v>1448260.460797036</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1448260.460797035</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1448260.460797035</v>
       </c>
       <c r="O2" t="n">
         <v>1448260.460797037</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337884</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566943.0001304756</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658208</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463365</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.0876296873</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286018</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604943</v>
+        <v>466508.6099301401</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>581130.2617157191</v>
+        <v>587631.6266486961</v>
       </c>
       <c r="C6" t="n">
-        <v>814237.1839032074</v>
+        <v>820738.548836185</v>
       </c>
       <c r="D6" t="n">
-        <v>816248.8313190319</v>
+        <v>822750.1962520087</v>
       </c>
       <c r="E6" t="n">
-        <v>294826.9320008595</v>
+        <v>301289.9231312141</v>
       </c>
       <c r="F6" t="n">
-        <v>886062.9948190829</v>
+        <v>892525.9859494375</v>
       </c>
       <c r="G6" t="n">
-        <v>887751.3843407357</v>
+        <v>894214.3754710903</v>
       </c>
       <c r="H6" t="n">
-        <v>889442.1172506987</v>
+        <v>895905.108381053</v>
       </c>
       <c r="I6" t="n">
-        <v>891135.2104512458</v>
+        <v>897598.2015816</v>
       </c>
       <c r="J6" t="n">
-        <v>504382.6810661707</v>
+        <v>510845.6721965242</v>
       </c>
       <c r="K6" t="n">
-        <v>894528.5464450044</v>
+        <v>900991.5375753582</v>
       </c>
       <c r="L6" t="n">
-        <v>896228.8241673488</v>
+        <v>902691.8152977021</v>
       </c>
       <c r="M6" t="n">
-        <v>801131.5320473158</v>
+        <v>807594.5231776693</v>
       </c>
       <c r="N6" t="n">
-        <v>899636.6881380794</v>
+        <v>906099.6792684338</v>
       </c>
       <c r="O6" t="n">
-        <v>644544.3107365422</v>
+        <v>651007.3018668969</v>
       </c>
       <c r="P6" t="n">
-        <v>903054.4183881248</v>
+        <v>909517.4095184795</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27002,13 +27002,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27106,13 +27106,13 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27512,28 +27512,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>62.57602625043802</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
         <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>190.0954123156894</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27572,13 +27572,13 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,37 +27591,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>343.8791148384516</v>
+        <v>336.5432435627184</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27645,22 +27645,22 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>196.5491832133428</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -27767,7 +27767,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>310.5719815352903</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
         <v>209.5726123064429</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27852,13 +27852,13 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>349.5166132815145</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27897,7 +27897,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>365.1835146730373</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -28004,7 +28004,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
         <v>209.5726123064429</v>
@@ -28031,16 +28031,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>398.9506152328534</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>222.8263550719547</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28071,22 +28071,22 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>373.7511368478467</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>353.8592638292932</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
@@ -28095,7 +28095,7 @@
         <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>359.1680042930194</v>
+      </c>
+      <c r="T10" t="n">
+        <v>209.2386648669134</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>400</v>
       </c>
-      <c r="U10" t="n">
-        <v>150.9483584875727</v>
-      </c>
-      <c r="V10" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28201,7 +28201,7 @@
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28229,13 +28229,13 @@
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="E12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28274,25 +28274,25 @@
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28463,22 +28463,22 @@
         <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>191.6509141932353</v>
@@ -28523,10 +28523,10 @@
         <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>321</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="X15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>321</v>
@@ -28630,7 +28630,7 @@
         <v>321</v>
       </c>
       <c r="F17" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G17" t="n">
         <v>321</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,22 +28697,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
         <v>321</v>
       </c>
       <c r="G18" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="H18" t="n">
         <v>321</v>
@@ -28751,7 +28751,7 @@
         <v>321</v>
       </c>
       <c r="T18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>321</v>
@@ -28760,10 +28760,10 @@
         <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="n">
         <v>321</v>
@@ -28934,19 +28934,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -29003,7 +29003,7 @@
         <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>147.4081841180273</v>
       </c>
     </row>
     <row r="22">
@@ -29095,7 +29095,7 @@
         <v>321</v>
       </c>
       <c r="C23" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="D23" t="n">
         <v>321</v>
@@ -29110,7 +29110,7 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29186,10 +29186,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="H24" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="I24" t="n">
         <v>191.6509141932353</v>
@@ -29347,7 +29347,7 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I26" t="n">
         <v>96.76634561233286</v>
@@ -29386,7 +29386,7 @@
         <v>321</v>
       </c>
       <c r="U26" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V26" t="n">
         <v>321</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
         <v>321</v>
@@ -29420,16 +29420,16 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>18.05909831126212</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29474,10 +29474,10 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
     </row>
     <row r="28">
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
         <v>96.76634561233286</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,22 +29645,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>226.036732227374</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H30" t="n">
         <v>321</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29821,10 +29821,10 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I32" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29885,7 +29885,7 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -29897,7 +29897,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
       <c r="H33" t="n">
         <v>321</v>
@@ -30027,7 +30027,7 @@
         <v>321</v>
       </c>
       <c r="X34" t="n">
-        <v>321.0000000000239</v>
+        <v>321</v>
       </c>
       <c r="Y34" t="n">
         <v>321</v>
@@ -30119,28 +30119,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C36" t="n">
         <v>321</v>
       </c>
       <c r="D36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H36" t="n">
         <v>321</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,16 +30164,16 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
         <v>321</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T36" t="n">
-        <v>96.68764642060955</v>
+        <v>321</v>
       </c>
       <c r="U36" t="n">
         <v>321</v>
@@ -30298,7 +30298,7 @@
         <v>321</v>
       </c>
       <c r="I38" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30328,7 +30328,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S38" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T38" t="n">
         <v>321</v>
@@ -30365,7 +30365,7 @@
         <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -30377,7 +30377,7 @@
         <v>321</v>
       </c>
       <c r="I39" t="n">
-        <v>18.05909831126212</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30416,7 +30416,7 @@
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>321</v>
@@ -30425,7 +30425,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
     </row>
     <row r="40">
@@ -30459,7 +30459,7 @@
         <v>321</v>
       </c>
       <c r="J40" t="n">
-        <v>321</v>
+        <v>321.0000000000385</v>
       </c>
       <c r="K40" t="n">
         <v>321</v>
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30593,16 +30593,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="F42" t="n">
         <v>321</v>
@@ -30614,7 +30614,7 @@
         <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,16 +30638,16 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>96.68764642060938</v>
+        <v>321</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U42" t="n">
         <v>321</v>
@@ -30696,7 +30696,7 @@
         <v>321</v>
       </c>
       <c r="J43" t="n">
-        <v>321</v>
+        <v>321.0000000000765</v>
       </c>
       <c r="K43" t="n">
         <v>321</v>
@@ -30732,7 +30732,7 @@
         <v>321</v>
       </c>
       <c r="V43" t="n">
-        <v>321.0000000000765</v>
+        <v>321</v>
       </c>
       <c r="W43" t="n">
         <v>321</v>
@@ -30772,7 +30772,7 @@
         <v>321</v>
       </c>
       <c r="I44" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="C45" t="n">
         <v>321</v>
@@ -30875,13 +30875,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -30896,10 +30896,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="Y45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -34743,25 +34743,25 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>52.1599296482412</v>
+      </c>
+      <c r="L2" t="n">
+        <v>306.7289592406477</v>
+      </c>
+      <c r="M2" t="n">
         <v>374</v>
       </c>
-      <c r="K2" t="n">
-        <v>52.15992964824119</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>374</v>
-      </c>
-      <c r="M2" t="n">
-        <v>248.0502805878619</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
         <v>374</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>58.34289678289618</v>
+        <v>51.00702550716294</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,22 +34931,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>300.2102102361031</v>
       </c>
       <c r="K5" t="n">
         <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>374</v>
       </c>
       <c r="M5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35138,13 +35138,13 @@
         <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>327.251828380033</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35183,7 +35183,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>77.71816182357487</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35226,7 +35226,7 @@
         <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>248.0502805878618</v>
+        <v>374</v>
       </c>
       <c r="N8" t="n">
         <v>374</v>
@@ -35238,7 +35238,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>248.0502805878619</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35357,22 +35357,22 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>88.21491879229129</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>108.9993254139927</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35381,7 +35381,7 @@
         <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,13 +35457,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="L11" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>649</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N11" t="n">
         <v>649</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35691,16 +35691,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
-        <v>609.8778844919133</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L14" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>60.29262328527617</v>
       </c>
       <c r="N14" t="n">
         <v>649</v>
@@ -35712,7 +35712,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35943,13 +35943,13 @@
         <v>649</v>
       </c>
       <c r="O17" t="n">
-        <v>596.7236430585247</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P17" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>433.9659648939237</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36174,7 +36174,7 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>490.597359871433</v>
       </c>
       <c r="N20" t="n">
         <v>649</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>433.9659648939237</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36411,16 +36411,16 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M23" t="n">
+        <v>490.597359871433</v>
+      </c>
+      <c r="N23" t="n">
         <v>649</v>
-      </c>
-      <c r="N23" t="n">
-        <v>40.17514405185732</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
         <v>592.3686050224903</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L26" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
+        <v>609.8778844919133</v>
+      </c>
+      <c r="N26" t="n">
         <v>649</v>
-      </c>
-      <c r="N26" t="n">
-        <v>60.29262328527629</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36660,7 +36660,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36876,7 +36876,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
         <v>175.9119195979899</v>
@@ -36885,10 +36885,10 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
-        <v>202.2390124881908</v>
+        <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>649</v>
+        <v>40.17514405185732</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -36897,7 +36897,7 @@
         <v>649</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37119,13 +37119,13 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L32" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M32" t="n">
         <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>490.5973598714331</v>
+        <v>649</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>592.3686050224903</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37313,7 +37313,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X34" t="n">
-        <v>73.55635456991639</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y34" t="n">
         <v>33.53464715053764</v>
@@ -37350,10 +37350,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L35" t="n">
         <v>218.2342914572864</v>
@@ -37362,16 +37362,16 @@
         <v>649</v>
       </c>
       <c r="N35" t="n">
+        <v>123.6355626565145</v>
+      </c>
+      <c r="O35" t="n">
         <v>649</v>
-      </c>
-      <c r="O35" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P35" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.661228307766413</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37590,25 +37590,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K38" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
-        <v>649</v>
+        <v>216.0870636498472</v>
       </c>
       <c r="N38" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P38" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J40" t="n">
-        <v>329.5882314919611</v>
+        <v>329.5882314919996</v>
       </c>
       <c r="K40" t="n">
         <v>104.5500458709881</v>
@@ -37827,13 +37827,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="N41" t="n">
         <v>649</v>
@@ -37982,7 +37982,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J43" t="n">
-        <v>329.5882314919611</v>
+        <v>329.5882314920376</v>
       </c>
       <c r="K43" t="n">
         <v>104.5500458709881</v>
@@ -38018,7 +38018,7 @@
         <v>170.0754447911158</v>
       </c>
       <c r="V43" t="n">
-        <v>121.8296897838602</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W43" t="n">
         <v>94.62719016129032</v>
@@ -38064,22 +38064,22 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
-        <v>364.535718696235</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
         <v>649</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O44" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
